--- a/KatalonData/ABPTestDataDemo/SchedulePaymentABP_DCF_Demo.xlsx
+++ b/KatalonData/ABPTestDataDemo/SchedulePaymentABP_DCF_Demo.xlsx
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="259" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="419" uniqueCount="86">
   <si>
     <t>Result</t>
   </si>
@@ -384,6 +384,126 @@
   </si>
   <si>
     <t>Wed Dec 31 21:16:58 IST 2025</t>
+  </si>
+  <si>
+    <t>Tue Jul 07 00:00:45 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Jul 07 00:01:51 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Jul 07 00:03:12 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Jul 07 00:04:32 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Jul 07 00:06:16 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Jul 07 00:07:09 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Jul 07 00:07:56 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Jul 07 00:08:45 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Jul 07 00:09:34 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Jul 07 00:10:20 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Jul 07 00:11:10 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Jul 07 00:11:51 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Jul 07 00:12:41 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Jul 07 00:13:32 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Jul 07 00:14:19 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Jul 07 00:16:19 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Jul 07 00:17:09 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Jul 07 00:18:03 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Jul 07 00:18:59 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Jul 07 00:19:49 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Jul 07 00:35:01 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Jul 07 00:35:48 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Jul 07 00:36:42 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Jul 07 00:37:37 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Jul 07 00:38:26 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Jul 07 00:39:12 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Jul 07 00:40:02 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Jul 07 00:40:48 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Jul 07 00:41:33 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Jul 07 00:43:21 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Jul 07 00:44:09 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Jul 07 00:44:59 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Jul 07 00:45:43 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Jul 07 00:46:29 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Jul 07 00:47:09 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Jul 07 00:47:50 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Jul 07 00:48:35 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Jul 07 00:49:19 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Jul 07 00:50:03 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Jul 07 00:50:53 IST 2026</t>
   </si>
 </sst>
 </file>
@@ -766,7 +886,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Q2"/>
+  <dimension ref="A1:P2"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
     <row ht="43.5" r="1" spans="1:16" x14ac:dyDescent="0.35">
@@ -791,13 +911,13 @@
       <c r="G1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H1" t="s">
+      <c r="H1" t="s" s="0">
         <v>7</v>
       </c>
-      <c r="I1" t="s">
+      <c r="I1" t="s" s="0">
         <v>8</v>
       </c>
-      <c r="J1" t="s">
+      <c r="J1" t="s" s="0">
         <v>9</v>
       </c>
       <c r="K1" s="3" t="s">
@@ -820,11 +940,11 @@
       </c>
     </row>
     <row ht="409.5" r="2" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A2" t="s">
+      <c r="A2" t="s" s="0">
         <v>14</v>
       </c>
-      <c r="B2" t="s">
-        <v>29</v>
+      <c r="B2" t="s" s="0">
+        <v>53</v>
       </c>
       <c r="C2" s="4"/>
       <c r="D2" s="5" t="s">
@@ -836,17 +956,17 @@
       <c r="F2" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="G2" t="str">
+      <c r="G2" t="str" s="0">
         <f>"Smith"</f>
         <v>Smith</v>
       </c>
-      <c r="H2" t="s">
+      <c r="H2" t="s" s="0">
         <v>18</v>
       </c>
-      <c r="I2" t="s">
+      <c r="I2" t="s" s="0">
         <v>19</v>
       </c>
-      <c r="J2" t="s">
+      <c r="J2" t="s" s="0">
         <v>20</v>
       </c>
       <c r="K2" s="6" t="s">
@@ -910,7 +1030,7 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F7A5AD8E-8FB3-4E0D-8FB3-58E3B5B29B16}">
-  <dimension ref="A1:Q2"/>
+  <dimension ref="A1:P2"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
     <row ht="43.5" r="1" spans="1:16" x14ac:dyDescent="0.35">
@@ -935,13 +1055,13 @@
       <c r="G1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H1" t="s">
+      <c r="H1" t="s" s="0">
         <v>7</v>
       </c>
-      <c r="I1" t="s">
+      <c r="I1" t="s" s="0">
         <v>8</v>
       </c>
-      <c r="J1" t="s">
+      <c r="J1" t="s" s="0">
         <v>9</v>
       </c>
       <c r="K1" s="3" t="s">
@@ -964,13 +1084,13 @@
       </c>
     </row>
     <row ht="409.5" r="2" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A2" t="s">
+      <c r="A2" t="s" s="0">
         <v>14</v>
       </c>
-      <c r="B2" t="s">
-        <v>38</v>
-      </c>
-      <c r="C2" t="s">
+      <c r="B2" t="s" s="0">
+        <v>73</v>
+      </c>
+      <c r="C2" t="s" s="0">
         <v>21</v>
       </c>
       <c r="D2" s="5" t="s">
@@ -982,17 +1102,17 @@
       <c r="F2" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="G2" t="str">
+      <c r="G2" t="str" s="0">
         <f>"CarlosJacinta"</f>
         <v>CarlosJacinta</v>
       </c>
-      <c r="H2" t="s">
+      <c r="H2" t="s" s="0">
         <v>18</v>
       </c>
-      <c r="I2" t="s">
+      <c r="I2" t="s" s="0">
         <v>19</v>
       </c>
-      <c r="J2" t="s">
+      <c r="J2" t="s" s="0">
         <v>20</v>
       </c>
       <c r="K2" s="6" t="s">
@@ -1052,7 +1172,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2865416F-EAD8-4226-BA0B-0AD26ABF0604}">
-  <dimension ref="A1:Q2"/>
+  <dimension ref="A1:P2"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="11" max="11" customWidth="true" width="24.81640625" collapsed="true"/>
@@ -1080,13 +1200,13 @@
       <c r="G1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H1" t="s">
+      <c r="H1" t="s" s="0">
         <v>7</v>
       </c>
-      <c r="I1" t="s">
+      <c r="I1" t="s" s="0">
         <v>8</v>
       </c>
-      <c r="J1" t="s">
+      <c r="J1" t="s" s="0">
         <v>9</v>
       </c>
       <c r="K1" s="3" t="s">
@@ -1109,11 +1229,11 @@
       </c>
     </row>
     <row ht="409.5" r="2" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A2" t="s">
+      <c r="A2" t="s" s="0">
         <v>14</v>
       </c>
-      <c r="B2" t="s">
-        <v>37</v>
+      <c r="B2" t="s" s="0">
+        <v>69</v>
       </c>
       <c r="C2" s="4"/>
       <c r="D2" s="5" t="s">
@@ -1125,17 +1245,17 @@
       <c r="F2" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="G2" t="str">
+      <c r="G2" t="str" s="0">
         <f>"CarlosJacinta"</f>
         <v>CarlosJacinta</v>
       </c>
-      <c r="H2" t="s">
+      <c r="H2" t="s" s="0">
         <v>18</v>
       </c>
-      <c r="I2" t="s">
+      <c r="I2" t="s" s="0">
         <v>19</v>
       </c>
-      <c r="J2" t="s">
+      <c r="J2" t="s" s="0">
         <v>22</v>
       </c>
       <c r="K2" s="6" t="s">
@@ -1195,7 +1315,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FA3A7C80-3096-4B80-A8BF-99672E759DAB}">
-  <dimension ref="A1:Q2"/>
+  <dimension ref="A1:P2"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="11" max="11" customWidth="true" width="31.36328125" collapsed="true"/>
@@ -1223,13 +1343,13 @@
       <c r="G1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H1" t="s">
+      <c r="H1" t="s" s="0">
         <v>7</v>
       </c>
-      <c r="I1" t="s">
+      <c r="I1" t="s" s="0">
         <v>8</v>
       </c>
-      <c r="J1" t="s">
+      <c r="J1" t="s" s="0">
         <v>9</v>
       </c>
       <c r="K1" s="3" t="s">
@@ -1252,11 +1372,11 @@
       </c>
     </row>
     <row ht="409.5" r="2" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A2" t="s">
+      <c r="A2" t="s" s="0">
         <v>14</v>
       </c>
-      <c r="B2" t="s">
-        <v>27</v>
+      <c r="B2" t="s" s="0">
+        <v>49</v>
       </c>
       <c r="C2" s="4"/>
       <c r="D2" s="5" t="s">
@@ -1268,17 +1388,17 @@
       <c r="F2" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="G2" t="str">
+      <c r="G2" t="str" s="0">
         <f>"Smith"</f>
         <v>Smith</v>
       </c>
-      <c r="H2" t="s">
+      <c r="H2" t="s" s="0">
         <v>18</v>
       </c>
-      <c r="I2" t="s">
+      <c r="I2" t="s" s="0">
         <v>19</v>
       </c>
-      <c r="J2" t="s">
+      <c r="J2" t="s" s="0">
         <v>22</v>
       </c>
       <c r="K2" s="6" t="s">
@@ -1338,7 +1458,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A397DB6E-BC66-4CE5-A0EA-21E31C3C1269}">
-  <dimension ref="A1:Q2"/>
+  <dimension ref="A1:P2"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="11" max="11" customWidth="true" width="27.6328125" collapsed="true"/>
@@ -1366,13 +1486,13 @@
       <c r="G1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H1" t="s">
+      <c r="H1" t="s" s="0">
         <v>7</v>
       </c>
-      <c r="I1" t="s">
+      <c r="I1" t="s" s="0">
         <v>8</v>
       </c>
-      <c r="J1" t="s">
+      <c r="J1" t="s" s="0">
         <v>9</v>
       </c>
       <c r="K1" s="3" t="s">
@@ -1395,11 +1515,11 @@
       </c>
     </row>
     <row ht="409.5" r="2" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A2" t="s">
+      <c r="A2" t="s" s="0">
         <v>14</v>
       </c>
-      <c r="B2" t="s">
-        <v>40</v>
+      <c r="B2" t="s" s="0">
+        <v>77</v>
       </c>
       <c r="C2" s="4"/>
       <c r="D2" s="5" t="s">
@@ -1411,17 +1531,17 @@
       <c r="F2" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="G2" t="str">
+      <c r="G2" t="str" s="0">
         <f>"CarlosJacinta"</f>
         <v>CarlosJacinta</v>
       </c>
-      <c r="H2" t="s">
+      <c r="H2" t="s" s="0">
         <v>18</v>
       </c>
-      <c r="I2" t="s">
+      <c r="I2" t="s" s="0">
         <v>23</v>
       </c>
-      <c r="J2" t="s">
+      <c r="J2" t="s" s="0">
         <v>20</v>
       </c>
       <c r="K2" s="6" t="s">
@@ -1481,7 +1601,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4BF2A858-8568-405F-B1FE-A4DB3A2B6FAB}">
-  <dimension ref="A1:Q2"/>
+  <dimension ref="A1:P2"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="11" max="11" customWidth="true" width="24.7265625" collapsed="true"/>
@@ -1509,13 +1629,13 @@
       <c r="G1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H1" t="s">
+      <c r="H1" t="s" s="0">
         <v>7</v>
       </c>
-      <c r="I1" t="s">
+      <c r="I1" t="s" s="0">
         <v>8</v>
       </c>
-      <c r="J1" t="s">
+      <c r="J1" t="s" s="0">
         <v>9</v>
       </c>
       <c r="K1" s="3" t="s">
@@ -1538,11 +1658,11 @@
       </c>
     </row>
     <row ht="409.5" r="2" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A2" t="s">
+      <c r="A2" t="s" s="0">
         <v>14</v>
       </c>
-      <c r="B2" t="s">
-        <v>31</v>
+      <c r="B2" t="s" s="0">
+        <v>57</v>
       </c>
       <c r="C2" s="4"/>
       <c r="D2" s="5" t="s">
@@ -1554,17 +1674,17 @@
       <c r="F2" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="G2" t="str">
+      <c r="G2" t="str" s="0">
         <f>"Smith"</f>
         <v>Smith</v>
       </c>
-      <c r="H2" t="s">
+      <c r="H2" t="s" s="0">
         <v>18</v>
       </c>
-      <c r="I2" t="s">
+      <c r="I2" t="s" s="0">
         <v>23</v>
       </c>
-      <c r="J2" t="s">
+      <c r="J2" t="s" s="0">
         <v>20</v>
       </c>
       <c r="K2" s="6" t="s">
@@ -1625,7 +1745,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9F06328A-9DEA-4031-BF6E-3E1679D9E636}">
-  <dimension ref="A1:Q2"/>
+  <dimension ref="A1:P2"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="11" max="11" customWidth="true" width="20.26953125" collapsed="true"/>
@@ -1653,13 +1773,13 @@
       <c r="G1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H1" t="s">
+      <c r="H1" t="s" s="0">
         <v>7</v>
       </c>
-      <c r="I1" t="s">
+      <c r="I1" t="s" s="0">
         <v>8</v>
       </c>
-      <c r="J1" t="s">
+      <c r="J1" t="s" s="0">
         <v>9</v>
       </c>
       <c r="K1" s="3" t="s">
@@ -1682,11 +1802,11 @@
       </c>
     </row>
     <row ht="409.5" r="2" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A2" t="s">
+      <c r="A2" t="s" s="0">
         <v>14</v>
       </c>
-      <c r="B2" t="s">
-        <v>45</v>
+      <c r="B2" t="s" s="0">
+        <v>85</v>
       </c>
       <c r="C2" s="4"/>
       <c r="D2" s="5" t="s">
@@ -1698,17 +1818,17 @@
       <c r="F2" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="G2" t="str">
+      <c r="G2" t="str" s="0">
         <f>"CarlosJacinta"</f>
         <v>CarlosJacinta</v>
       </c>
-      <c r="H2" t="s">
+      <c r="H2" t="s" s="0">
         <v>24</v>
       </c>
-      <c r="I2" t="s">
+      <c r="I2" t="s" s="0">
         <v>23</v>
       </c>
-      <c r="J2" t="s">
+      <c r="J2" t="s" s="0">
         <v>20</v>
       </c>
       <c r="K2" s="6" t="s">
@@ -1768,7 +1888,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{900F5C47-9A3E-42DC-8852-58A42D0C9EFE}">
-  <dimension ref="A1:Q2"/>
+  <dimension ref="A1:P2"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="11" max="11" customWidth="true" width="26.6328125" collapsed="true"/>
@@ -1796,13 +1916,13 @@
       <c r="G1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H1" t="s">
+      <c r="H1" t="s" s="0">
         <v>7</v>
       </c>
-      <c r="I1" t="s">
+      <c r="I1" t="s" s="0">
         <v>8</v>
       </c>
-      <c r="J1" t="s">
+      <c r="J1" t="s" s="0">
         <v>9</v>
       </c>
       <c r="K1" s="3" t="s">
@@ -1825,11 +1945,11 @@
       </c>
     </row>
     <row ht="409.5" r="2" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A2" t="s">
+      <c r="A2" t="s" s="0">
         <v>14</v>
       </c>
-      <c r="B2" t="s">
-        <v>35</v>
+      <c r="B2" t="s" s="0">
+        <v>65</v>
       </c>
       <c r="C2" s="4"/>
       <c r="D2" s="5" t="s">
@@ -1841,17 +1961,17 @@
       <c r="F2" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="G2" t="str">
+      <c r="G2" t="str" s="0">
         <f>"Smith"</f>
         <v>Smith</v>
       </c>
-      <c r="H2" t="s">
+      <c r="H2" t="s" s="0">
         <v>24</v>
       </c>
-      <c r="I2" t="s">
+      <c r="I2" t="s" s="0">
         <v>23</v>
       </c>
-      <c r="J2" t="s">
+      <c r="J2" t="s" s="0">
         <v>20</v>
       </c>
       <c r="K2" s="6" t="s">
@@ -1911,7 +2031,7 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{10510DE0-0B5B-490D-A8EE-5AFB1CF2AE1D}">
-  <dimension ref="A1:Q2"/>
+  <dimension ref="A1:P2"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="11" max="11" customWidth="true" width="20.1796875" collapsed="true"/>
@@ -1939,13 +2059,13 @@
       <c r="G1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H1" t="s">
+      <c r="H1" t="s" s="0">
         <v>7</v>
       </c>
-      <c r="I1" t="s">
+      <c r="I1" t="s" s="0">
         <v>8</v>
       </c>
-      <c r="J1" t="s">
+      <c r="J1" t="s" s="0">
         <v>9</v>
       </c>
       <c r="K1" s="3" t="s">
@@ -1968,11 +2088,11 @@
       </c>
     </row>
     <row ht="409.5" r="2" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A2" t="s">
+      <c r="A2" t="s" s="0">
         <v>14</v>
       </c>
-      <c r="B2" t="s">
-        <v>42</v>
+      <c r="B2" t="s" s="0">
+        <v>81</v>
       </c>
       <c r="C2" s="4"/>
       <c r="D2" s="5" t="s">
@@ -1984,17 +2104,17 @@
       <c r="F2" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="G2" t="str">
+      <c r="G2" t="str" s="0">
         <f>"CarlosJacinta"</f>
         <v>CarlosJacinta</v>
       </c>
-      <c r="H2" t="s">
+      <c r="H2" t="s" s="0">
         <v>24</v>
       </c>
-      <c r="I2" t="s">
+      <c r="I2" t="s" s="0">
         <v>19</v>
       </c>
-      <c r="J2" t="s">
+      <c r="J2" t="s" s="0">
         <v>20</v>
       </c>
       <c r="K2" s="6" t="s">
@@ -2054,7 +2174,7 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{57EEE3BC-AF45-4450-AB4B-7E9300EF985A}">
-  <dimension ref="A1:Q2"/>
+  <dimension ref="A1:P2"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="11" max="11" customWidth="true" width="21.26953125" collapsed="true"/>
@@ -2082,13 +2202,13 @@
       <c r="G1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H1" t="s">
+      <c r="H1" t="s" s="0">
         <v>7</v>
       </c>
-      <c r="I1" t="s">
+      <c r="I1" t="s" s="0">
         <v>8</v>
       </c>
-      <c r="J1" t="s">
+      <c r="J1" t="s" s="0">
         <v>9</v>
       </c>
       <c r="K1" s="3" t="s">
@@ -2111,11 +2231,11 @@
       </c>
     </row>
     <row ht="409.5" r="2" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A2" t="s">
+      <c r="A2" t="s" s="0">
         <v>14</v>
       </c>
-      <c r="B2" t="s">
-        <v>33</v>
+      <c r="B2" t="s" s="0">
+        <v>61</v>
       </c>
       <c r="C2" s="4"/>
       <c r="D2" s="5" t="s">
@@ -2127,17 +2247,17 @@
       <c r="F2" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="G2" t="str">
+      <c r="G2" t="str" s="0">
         <f>"Smith"</f>
         <v>Smith</v>
       </c>
-      <c r="H2" t="s">
+      <c r="H2" t="s" s="0">
         <v>24</v>
       </c>
-      <c r="I2" t="s">
+      <c r="I2" t="s" s="0">
         <v>19</v>
       </c>
-      <c r="J2" t="s">
+      <c r="J2" t="s" s="0">
         <v>20</v>
       </c>
       <c r="K2" s="6" t="s">

--- a/KatalonData/ABPTestDataDemo/SchedulePaymentABP_DCF_Demo.xlsx
+++ b/KatalonData/ABPTestDataDemo/SchedulePaymentABP_DCF_Demo.xlsx
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="419" uniqueCount="86">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="463" uniqueCount="97">
   <si>
     <t>Result</t>
   </si>
@@ -504,6 +504,39 @@
   </si>
   <si>
     <t>Tue Jul 07 00:50:53 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jul 24 17:36:14 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jul 24 17:38:15 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jul 24 17:39:38 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jul 24 17:42:00 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jul 24 17:43:53 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jul 24 17:45:54 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jul 24 17:53:47 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jul 24 17:55:12 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jul 24 17:56:18 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jul 24 17:58:55 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jul 24 18:00:36 IST 2026</t>
   </si>
 </sst>
 </file>
@@ -944,7 +977,7 @@
         <v>14</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>53</v>
+        <v>87</v>
       </c>
       <c r="C2" s="4"/>
       <c r="D2" s="5" t="s">
@@ -1088,7 +1121,7 @@
         <v>14</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>73</v>
+        <v>93</v>
       </c>
       <c r="C2" t="s" s="0">
         <v>21</v>
@@ -1233,7 +1266,7 @@
         <v>14</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>69</v>
+        <v>92</v>
       </c>
       <c r="C2" s="4"/>
       <c r="D2" s="5" t="s">
@@ -1376,7 +1409,7 @@
         <v>14</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>49</v>
+        <v>86</v>
       </c>
       <c r="C2" s="4"/>
       <c r="D2" s="5" t="s">
@@ -1519,7 +1552,7 @@
         <v>14</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>77</v>
+        <v>94</v>
       </c>
       <c r="C2" s="4"/>
       <c r="D2" s="5" t="s">
@@ -1662,7 +1695,7 @@
         <v>14</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>57</v>
+        <v>89</v>
       </c>
       <c r="C2" s="4"/>
       <c r="D2" s="5" t="s">
@@ -1806,7 +1839,7 @@
         <v>14</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="C2" s="4"/>
       <c r="D2" s="5" t="s">
@@ -1949,7 +1982,7 @@
         <v>14</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>65</v>
+        <v>91</v>
       </c>
       <c r="C2" s="4"/>
       <c r="D2" s="5" t="s">
@@ -2092,7 +2125,7 @@
         <v>14</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>81</v>
+        <v>95</v>
       </c>
       <c r="C2" s="4"/>
       <c r="D2" s="5" t="s">
@@ -2235,7 +2268,7 @@
         <v>14</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>61</v>
+        <v>90</v>
       </c>
       <c r="C2" s="4"/>
       <c r="D2" s="5" t="s">
